--- a/E/AIRMIN.xlsx
+++ b/E/AIRMIN.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="28">
   <si>
     <t/>
   </si>
   <si>
-    <t>10036631</t>
-  </si>
-  <si>
-    <t>AQUA AIR MINERAL19LT</t>
+    <t>10037807</t>
+  </si>
+  <si>
+    <t>AQUA GALON KOSONG</t>
   </si>
   <si>
     <t>AIRMIN</t>
@@ -28,28 +28,22 @@
     <t>1</t>
   </si>
   <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>RT</t>
+  </si>
+  <si>
+    <t>10004487</t>
+  </si>
+  <si>
+    <t>AQUA AIR MINERAL 200</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
     <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>10037807</t>
-  </si>
-  <si>
-    <t>AQUA GALON KOSONG</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>RT</t>
-  </si>
-  <si>
-    <t>10004487</t>
-  </si>
-  <si>
-    <t>AQUA AIR MINERAL 200</t>
-  </si>
-  <si>
-    <t>3</t>
   </si>
   <si>
     <t>10004335</t>
@@ -493,7 +487,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -537,18 +531,18 @@
         <v>4</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>3</v>
@@ -557,18 +551,18 @@
         <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -577,18 +571,18 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -597,18 +591,18 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -617,18 +611,18 @@
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
@@ -637,50 +631,30 @@
         <v>4</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E8" s="1" t="s">
-        <v>26</v>
-      </c>
       <c r="F8" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/E/AIRMIN.xlsx
+++ b/E/AIRMIN.xlsx
@@ -11,23 +11,32 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="30">
   <si>
     <t/>
   </si>
   <si>
+    <t>10036631</t>
+  </si>
+  <si>
+    <t>AQUA AIR MINERAL19LT</t>
+  </si>
+  <si>
+    <t>AIRMIN</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
     <t>10037807</t>
   </si>
   <si>
     <t>AQUA GALON KOSONG</t>
   </si>
   <si>
-    <t>AIRMIN</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
     <t>2</t>
   </si>
   <si>
@@ -41,9 +50,6 @@
   </si>
   <si>
     <t>3</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
   </si>
   <si>
     <t>10004335</t>
@@ -487,7 +493,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -531,130 +537,150 @@
         <v>4</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="F4" s="1" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="F5" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="F6" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="C7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>24</v>
-      </c>
       <c r="F7" s="1" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="F8" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1" t="s">
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F9" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/E/AIRMIN.xlsx
+++ b/E/AIRMIN.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="31">
   <si>
     <t/>
   </si>
@@ -101,6 +101,9 @@
   </si>
   <si>
     <t>AQUA MNERAL 24X220ML</t>
+  </si>
+  <si>
+    <t>8</t>
   </si>
 </sst>
 </file>
@@ -674,10 +677,10 @@
         <v>3</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>5</v>

--- a/E/AIRMIN.xlsx
+++ b/E/AIRMIN.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="34">
   <si>
     <t/>
   </si>
@@ -104,6 +104,15 @@
   </si>
   <si>
     <t>8</t>
+  </si>
+  <si>
+    <t>20134073</t>
+  </si>
+  <si>
+    <t>CLUB AIR MNRAL 220ML</t>
+  </si>
+  <si>
+    <t>9</t>
   </si>
 </sst>
 </file>
@@ -496,7 +505,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -686,6 +695,26 @@
         <v>5</v>
       </c>
     </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
